--- a/Week1_Day2.xlsx
+++ b/Week1_Day2.xlsx
@@ -8,21 +8,38 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/keerthiganesan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A529F6D8-4322-6C48-8B47-3AD0269D05B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{37DC44E4-3ED9-D74E-9727-6567440B7286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Multimodal Models Comparison" sheetId="1" r:id="rId1"/>
     <sheet name="Model_Input_Output_Context" sheetId="2" r:id="rId2"/>
     <sheet name="Groq_Model" sheetId="3" r:id="rId3"/>
+    <sheet name="Token_Generator" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="108">
   <si>
     <t>Provider</t>
   </si>
@@ -319,6 +336,33 @@
   </si>
   <si>
     <t>Strong reasoning</t>
+  </si>
+  <si>
+    <t>Text Length (characters)</t>
+  </si>
+  <si>
+    <t>Est. Tokens (Eng)</t>
+  </si>
+  <si>
+    <t>Est. Tokens (Code)</t>
+  </si>
+  <si>
+    <t>Est. Tokens (Indic)</t>
+  </si>
+  <si>
+    <t>Input $/1M</t>
+  </si>
+  <si>
+    <t>Output $/1M</t>
+  </si>
+  <si>
+    <t>Tokens Used</t>
+  </si>
+  <si>
+    <t>Input Cost ($)</t>
+  </si>
+  <si>
+    <t>Output Cost ($)</t>
   </si>
 </sst>
 </file>
@@ -380,6 +424,32 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Calculator"/>
+      <sheetName val="Model Comparison"/>
+      <sheetName val="Summary"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="B2">
+            <v>250</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1345,6 +1415,188 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E4A608-10F0-0B42-BD00-B0D415EC4AFE}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="8.83203125"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2">
+        <f>A2/4</f>
+        <v>250</v>
+      </c>
+      <c r="C2">
+        <f>A2/3</f>
+        <v>333.33333333333331</v>
+      </c>
+      <c r="D2">
+        <f>A2/2</f>
+        <v>500</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>0.4</v>
+      </c>
+      <c r="G2">
+        <v>1.6</v>
+      </c>
+      <c r="H2">
+        <f>[1]Calculator!B2</f>
+        <v>250</v>
+      </c>
+      <c r="I2">
+        <f>H2/1000000*F2</f>
+        <v>1E-4</v>
+      </c>
+      <c r="J2">
+        <f>H2/1000000*G2</f>
+        <v>4.0000000000000002E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>2.5</v>
+      </c>
+      <c r="G3">
+        <v>10</v>
+      </c>
+      <c r="H3">
+        <f>[1]Calculator!B2</f>
+        <v>250</v>
+      </c>
+      <c r="I3">
+        <f>H3/1000000*F3</f>
+        <v>6.2500000000000001E-4</v>
+      </c>
+      <c r="J3">
+        <f>H3/1000000*G3</f>
+        <v>2.5000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>0.25</v>
+      </c>
+      <c r="G4">
+        <v>0.38</v>
+      </c>
+      <c r="H4">
+        <f>[1]Calculator!B2</f>
+        <v>250</v>
+      </c>
+      <c r="I4">
+        <f>H4/1000000*F4</f>
+        <v>6.2500000000000001E-5</v>
+      </c>
+      <c r="J4">
+        <f>H4/1000000*G4</f>
+        <v>9.5000000000000005E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <v>15</v>
+      </c>
+      <c r="H5">
+        <f>[1]Calculator!B2</f>
+        <v>250</v>
+      </c>
+      <c r="I5">
+        <f>H5/1000000*F5</f>
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="J5">
+        <f>H5/1000000*G5</f>
+        <v>3.7499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>12</v>
+      </c>
+      <c r="H6">
+        <f>[1]Calculator!B2</f>
+        <v>250</v>
+      </c>
+      <c r="I6">
+        <f>H6/1000000*F6</f>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="J6">
+        <f>H6/1000000*G6</f>
+        <v>3.0000000000000001E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4ca0b373-e9b1-4578-8e53-53d6aaa79771}" enabled="1" method="Standard" siteId="{f9465cb1-7889-4d9a-b552-fdd0addf0eb1}" contentBits="0" removed="0"/>
